--- a/artfynd/A 49848-2019 artfynd.xlsx
+++ b/artfynd/A 49848-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49848-2019 artfynd.xlsx
+++ b/artfynd/A 49848-2019 artfynd.xlsx
@@ -1327,10 +1327,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121993748</v>
+        <v>121986547</v>
       </c>
       <c r="B7" t="n">
-        <v>95722</v>
+        <v>58245</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1339,25 +1339,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>100141</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>622274</v>
+        <v>622415</v>
       </c>
       <c r="R7" t="n">
-        <v>6616320</v>
+        <v>6616365</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1397,12 +1397,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1417,22 +1422,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121986547</v>
+        <v>121986581</v>
       </c>
       <c r="B8" t="n">
-        <v>58245</v>
+        <v>90799</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1441,25 +1446,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100141</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1469,10 +1474,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622415</v>
+        <v>622074</v>
       </c>
       <c r="R8" t="n">
-        <v>6616365</v>
+        <v>6616112</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1499,17 +1504,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>på död tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1536,10 +1541,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121993752</v>
+        <v>121986550</v>
       </c>
       <c r="B9" t="n">
-        <v>4770</v>
+        <v>58245</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1552,21 +1557,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100299</v>
+        <v>100141</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1576,10 +1581,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>622154</v>
+        <v>622418</v>
       </c>
       <c r="R9" t="n">
-        <v>6616068</v>
+        <v>6616372</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1606,12 +1611,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1626,19 +1631,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121986572</v>
+        <v>121986570</v>
       </c>
       <c r="B10" t="n">
         <v>90799</v>
@@ -1678,10 +1683,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>622558</v>
+        <v>622531</v>
       </c>
       <c r="R10" t="n">
-        <v>6616401</v>
+        <v>6616428</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1740,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121986581</v>
+        <v>121986551</v>
       </c>
       <c r="B11" t="n">
-        <v>90799</v>
+        <v>58242</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1752,38 +1757,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>208242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>622074</v>
+        <v>622418</v>
       </c>
       <c r="R11" t="n">
-        <v>6616112</v>
+        <v>6616372</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1810,17 +1824,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>på död tall</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1847,10 +1856,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121986550</v>
+        <v>121986548</v>
       </c>
       <c r="B12" t="n">
-        <v>58245</v>
+        <v>58232</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1863,21 +1872,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100141</v>
+        <v>208250</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1949,10 +1958,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121987017</v>
+        <v>121986572</v>
       </c>
       <c r="B13" t="n">
-        <v>98175</v>
+        <v>90799</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1961,42 +1970,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622176</v>
+        <v>622558</v>
       </c>
       <c r="R13" t="n">
-        <v>6616076</v>
+        <v>6616401</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,12 +2028,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2055,10 +2060,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121986492</v>
+        <v>121993752</v>
       </c>
       <c r="B14" t="n">
-        <v>58242</v>
+        <v>4770</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,21 +2076,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>208242</v>
+        <v>100299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2095,10 +2100,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622554</v>
+        <v>622154</v>
       </c>
       <c r="R14" t="n">
-        <v>6616430</v>
+        <v>6616068</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2125,12 +2130,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,22 +2150,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121987026</v>
+        <v>121986552</v>
       </c>
       <c r="B15" t="n">
-        <v>98175</v>
+        <v>58245</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,42 +2174,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100141</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622127</v>
+        <v>622418</v>
       </c>
       <c r="R15" t="n">
-        <v>6616087</v>
+        <v>6616370</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2231,12 +2232,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1 hona</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,10 +2269,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121986553</v>
+        <v>121986568</v>
       </c>
       <c r="B16" t="n">
-        <v>58242</v>
+        <v>100441</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2279,43 +2285,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208242</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622418</v>
+        <v>622281</v>
       </c>
       <c r="R16" t="n">
-        <v>6616371</v>
+        <v>6616334</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2342,17 +2339,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2 hane och 4 hona</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2379,10 +2371,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121986552</v>
+        <v>121987018</v>
       </c>
       <c r="B17" t="n">
-        <v>58245</v>
+        <v>98175</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2391,38 +2383,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100141</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622418</v>
+        <v>622176</v>
       </c>
       <c r="R17" t="n">
-        <v>6616370</v>
+        <v>6616170</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2449,17 +2445,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>1 hona</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2486,10 +2477,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121986548</v>
+        <v>121987023</v>
       </c>
       <c r="B18" t="n">
-        <v>58232</v>
+        <v>98175</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2498,38 +2489,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>208250</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622418</v>
+        <v>622167</v>
       </c>
       <c r="R18" t="n">
-        <v>6616372</v>
+        <v>6616193</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2556,12 +2551,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,10 +2583,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121986571</v>
+        <v>121993748</v>
       </c>
       <c r="B19" t="n">
-        <v>90799</v>
+        <v>95722</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2604,21 +2599,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2628,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622553</v>
+        <v>622274</v>
       </c>
       <c r="R19" t="n">
-        <v>6616431</v>
+        <v>6616320</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2658,12 +2653,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2678,22 +2673,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121986568</v>
+        <v>121986554</v>
       </c>
       <c r="B20" t="n">
-        <v>100441</v>
+        <v>58232</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2706,34 +2701,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>208250</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>622281</v>
+        <v>622424</v>
       </c>
       <c r="R20" t="n">
-        <v>6616334</v>
+        <v>6616368</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2760,12 +2764,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2792,10 +2796,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121986551</v>
+        <v>121986571</v>
       </c>
       <c r="B21" t="n">
-        <v>58242</v>
+        <v>90799</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2804,47 +2808,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>208242</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>622418</v>
+        <v>622553</v>
       </c>
       <c r="R21" t="n">
-        <v>6616372</v>
+        <v>6616431</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2871,12 +2866,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2903,10 +2898,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121987018</v>
+        <v>121993750</v>
       </c>
       <c r="B22" t="n">
-        <v>98175</v>
+        <v>5173</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2915,42 +2910,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>622176</v>
+        <v>622261</v>
       </c>
       <c r="R22" t="n">
-        <v>6616170</v>
+        <v>6616264</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2977,12 +2968,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2997,19 +2988,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121987023</v>
+        <v>121987017</v>
       </c>
       <c r="B23" t="n">
         <v>98175</v>
@@ -3044,7 +3035,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3053,10 +3044,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>622167</v>
+        <v>622176</v>
       </c>
       <c r="R23" t="n">
-        <v>6616193</v>
+        <v>6616076</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3083,12 +3074,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3115,10 +3106,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121993750</v>
+        <v>121986553</v>
       </c>
       <c r="B24" t="n">
-        <v>5173</v>
+        <v>58242</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3131,34 +3122,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>208242</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>622261</v>
+        <v>622418</v>
       </c>
       <c r="R24" t="n">
-        <v>6616264</v>
+        <v>6616371</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3185,12 +3185,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>2 hane och 4 hona</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3205,19 +3210,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121987024</v>
+        <v>121987026</v>
       </c>
       <c r="B25" t="n">
         <v>98175</v>
@@ -3261,10 +3266,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>622203</v>
+        <v>622127</v>
       </c>
       <c r="R25" t="n">
-        <v>6616185</v>
+        <v>6616087</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3291,12 +3296,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3323,10 +3328,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121986554</v>
+        <v>121986492</v>
       </c>
       <c r="B26" t="n">
-        <v>58232</v>
+        <v>58242</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3339,43 +3344,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>622424</v>
+        <v>622554</v>
       </c>
       <c r="R26" t="n">
-        <v>6616368</v>
+        <v>6616430</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3402,12 +3398,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3434,10 +3430,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121986570</v>
+        <v>121987024</v>
       </c>
       <c r="B27" t="n">
-        <v>90799</v>
+        <v>98175</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3446,38 +3442,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>622531</v>
+        <v>622203</v>
       </c>
       <c r="R27" t="n">
-        <v>6616428</v>
+        <v>6616185</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 49848-2019 artfynd.xlsx
+++ b/artfynd/A 49848-2019 artfynd.xlsx
@@ -3328,10 +3328,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121986492</v>
+        <v>121987024</v>
       </c>
       <c r="B26" t="n">
-        <v>58242</v>
+        <v>98175</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3340,38 +3340,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>208242</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>622554</v>
+        <v>622203</v>
       </c>
       <c r="R26" t="n">
-        <v>6616430</v>
+        <v>6616185</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3398,12 +3402,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3430,10 +3434,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121987024</v>
+        <v>121986492</v>
       </c>
       <c r="B27" t="n">
-        <v>98175</v>
+        <v>58242</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3442,42 +3446,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>208242</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>622203</v>
+        <v>622554</v>
       </c>
       <c r="R27" t="n">
-        <v>6616185</v>
+        <v>6616430</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3504,12 +3504,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 49848-2019 artfynd.xlsx
+++ b/artfynd/A 49848-2019 artfynd.xlsx
@@ -1327,10 +1327,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121986547</v>
+        <v>121993750</v>
       </c>
       <c r="B7" t="n">
-        <v>58245</v>
+        <v>5173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1343,21 +1343,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100141</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>622415</v>
+        <v>622261</v>
       </c>
       <c r="R7" t="n">
-        <v>6616365</v>
+        <v>6616264</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1397,17 +1397,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1422,22 +1417,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121986581</v>
+        <v>121986570</v>
       </c>
       <c r="B8" t="n">
-        <v>90799</v>
+        <v>90809</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1474,10 +1469,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622074</v>
+        <v>622531</v>
       </c>
       <c r="R8" t="n">
-        <v>6616112</v>
+        <v>6616428</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1504,17 +1499,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>på död tall</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1541,7 +1531,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121986550</v>
+        <v>121986552</v>
       </c>
       <c r="B9" t="n">
         <v>58245</v>
@@ -1584,7 +1574,7 @@
         <v>622418</v>
       </c>
       <c r="R9" t="n">
-        <v>6616372</v>
+        <v>6616370</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1617,6 +1607,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1 hona</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1643,10 +1638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121986570</v>
+        <v>121993748</v>
       </c>
       <c r="B10" t="n">
-        <v>90799</v>
+        <v>95732</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1659,21 +1654,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1683,10 +1678,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>622531</v>
+        <v>622274</v>
       </c>
       <c r="R10" t="n">
-        <v>6616428</v>
+        <v>6616320</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1713,12 +1708,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1733,22 +1728,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121986551</v>
+        <v>121986547</v>
       </c>
       <c r="B11" t="n">
-        <v>58242</v>
+        <v>58245</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1761,43 +1756,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>622418</v>
+        <v>622415</v>
       </c>
       <c r="R11" t="n">
-        <v>6616372</v>
+        <v>6616365</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1830,6 +1816,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1856,10 +1847,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121986548</v>
+        <v>121987018</v>
       </c>
       <c r="B12" t="n">
-        <v>58232</v>
+        <v>98185</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1868,38 +1859,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208250</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622418</v>
+        <v>622176</v>
       </c>
       <c r="R12" t="n">
-        <v>6616372</v>
+        <v>6616170</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1926,12 +1921,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1958,10 +1953,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121986572</v>
+        <v>121987023</v>
       </c>
       <c r="B13" t="n">
-        <v>90799</v>
+        <v>98185</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1970,38 +1965,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622558</v>
+        <v>622167</v>
       </c>
       <c r="R13" t="n">
-        <v>6616401</v>
+        <v>6616193</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2060,10 +2059,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121993752</v>
+        <v>121986572</v>
       </c>
       <c r="B14" t="n">
-        <v>4770</v>
+        <v>90809</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2072,25 +2071,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100299</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2100,10 +2099,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622154</v>
+        <v>622558</v>
       </c>
       <c r="R14" t="n">
-        <v>6616068</v>
+        <v>6616401</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,12 +2129,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,22 +2149,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121986552</v>
+        <v>121986581</v>
       </c>
       <c r="B15" t="n">
-        <v>58245</v>
+        <v>90809</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2174,25 +2173,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100141</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2202,10 +2201,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622418</v>
+        <v>622074</v>
       </c>
       <c r="R15" t="n">
-        <v>6616370</v>
+        <v>6616112</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,17 +2231,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>1 hona</t>
+          <t>på död tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2269,10 +2268,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121986568</v>
+        <v>121986548</v>
       </c>
       <c r="B16" t="n">
-        <v>100441</v>
+        <v>58232</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2285,21 +2284,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>208250</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2309,10 +2308,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622281</v>
+        <v>622418</v>
       </c>
       <c r="R16" t="n">
-        <v>6616334</v>
+        <v>6616372</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2339,12 +2338,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,10 +2370,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121987018</v>
+        <v>121986492</v>
       </c>
       <c r="B17" t="n">
-        <v>98175</v>
+        <v>58242</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2383,42 +2382,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>208242</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622176</v>
+        <v>622554</v>
       </c>
       <c r="R17" t="n">
-        <v>6616170</v>
+        <v>6616430</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2445,12 +2440,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,10 +2472,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121987023</v>
+        <v>121986571</v>
       </c>
       <c r="B18" t="n">
-        <v>98175</v>
+        <v>90809</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2489,42 +2484,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622167</v>
+        <v>622553</v>
       </c>
       <c r="R18" t="n">
-        <v>6616193</v>
+        <v>6616431</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2583,10 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121993748</v>
+        <v>121987017</v>
       </c>
       <c r="B19" t="n">
-        <v>95722</v>
+        <v>98185</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2595,38 +2586,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622274</v>
+        <v>622176</v>
       </c>
       <c r="R19" t="n">
-        <v>6616320</v>
+        <v>6616076</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2653,12 +2648,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2673,22 +2668,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121986554</v>
+        <v>121986550</v>
       </c>
       <c r="B20" t="n">
-        <v>58232</v>
+        <v>58245</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2701,43 +2696,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>208250</v>
+        <v>100141</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>622424</v>
+        <v>622418</v>
       </c>
       <c r="R20" t="n">
-        <v>6616368</v>
+        <v>6616372</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2796,10 +2782,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121986571</v>
+        <v>121987026</v>
       </c>
       <c r="B21" t="n">
-        <v>90799</v>
+        <v>98185</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2808,38 +2794,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>622553</v>
+        <v>622127</v>
       </c>
       <c r="R21" t="n">
-        <v>6616431</v>
+        <v>6616087</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2866,12 +2856,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2898,10 +2888,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121993750</v>
+        <v>121987024</v>
       </c>
       <c r="B22" t="n">
-        <v>5173</v>
+        <v>98185</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2910,38 +2900,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>622261</v>
+        <v>622203</v>
       </c>
       <c r="R22" t="n">
-        <v>6616264</v>
+        <v>6616185</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2968,12 +2962,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2988,22 +2982,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121987017</v>
+        <v>121986551</v>
       </c>
       <c r="B23" t="n">
-        <v>98175</v>
+        <v>58242</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3012,30 +3006,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>208242</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3044,10 +3043,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>622176</v>
+        <v>622418</v>
       </c>
       <c r="R23" t="n">
-        <v>6616076</v>
+        <v>6616372</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3074,12 +3073,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3222,10 +3221,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121987026</v>
+        <v>121986568</v>
       </c>
       <c r="B25" t="n">
-        <v>98175</v>
+        <v>100451</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3234,42 +3233,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>622127</v>
+        <v>622281</v>
       </c>
       <c r="R25" t="n">
-        <v>6616087</v>
+        <v>6616334</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3296,12 +3291,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3328,10 +3323,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121987024</v>
+        <v>121986554</v>
       </c>
       <c r="B26" t="n">
-        <v>98175</v>
+        <v>58232</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3340,30 +3335,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>208250</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>622203</v>
+        <v>622424</v>
       </c>
       <c r="R26" t="n">
-        <v>6616185</v>
+        <v>6616368</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3402,12 +3402,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3434,10 +3434,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121986492</v>
+        <v>121993752</v>
       </c>
       <c r="B27" t="n">
-        <v>58242</v>
+        <v>4770</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3450,21 +3450,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>208242</v>
+        <v>100299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>622554</v>
+        <v>622154</v>
       </c>
       <c r="R27" t="n">
-        <v>6616430</v>
+        <v>6616068</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3504,12 +3504,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3524,12 +3524,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 49848-2019 artfynd.xlsx
+++ b/artfynd/A 49848-2019 artfynd.xlsx
@@ -1327,10 +1327,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121993750</v>
+        <v>121986550</v>
       </c>
       <c r="B7" t="n">
-        <v>5173</v>
+        <v>58245</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1343,21 +1343,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>100141</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>622261</v>
+        <v>622418</v>
       </c>
       <c r="R7" t="n">
-        <v>6616264</v>
+        <v>6616372</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1417,22 +1417,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121986570</v>
+        <v>121987018</v>
       </c>
       <c r="B8" t="n">
-        <v>90809</v>
+        <v>98185</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1441,38 +1441,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622531</v>
+        <v>622176</v>
       </c>
       <c r="R8" t="n">
-        <v>6616428</v>
+        <v>6616170</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1499,12 +1503,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,10 +1535,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121986552</v>
+        <v>121987023</v>
       </c>
       <c r="B9" t="n">
-        <v>58245</v>
+        <v>98185</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1543,38 +1547,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100141</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>622418</v>
+        <v>622167</v>
       </c>
       <c r="R9" t="n">
-        <v>6616370</v>
+        <v>6616193</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1601,17 +1609,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>1 hona</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1638,10 +1641,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121993748</v>
+        <v>121986572</v>
       </c>
       <c r="B10" t="n">
-        <v>95732</v>
+        <v>90809</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1654,21 +1657,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1678,10 +1681,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>622274</v>
+        <v>622558</v>
       </c>
       <c r="R10" t="n">
-        <v>6616320</v>
+        <v>6616401</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1708,12 +1711,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,22 +1731,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121986547</v>
+        <v>121986492</v>
       </c>
       <c r="B11" t="n">
-        <v>58245</v>
+        <v>58242</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1756,21 +1759,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100141</v>
+        <v>208242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1780,10 +1783,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>622415</v>
+        <v>622554</v>
       </c>
       <c r="R11" t="n">
-        <v>6616365</v>
+        <v>6616430</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1810,17 +1813,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1847,10 +1845,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121987018</v>
+        <v>121986553</v>
       </c>
       <c r="B12" t="n">
-        <v>98185</v>
+        <v>58242</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1859,30 +1857,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>208242</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1891,10 +1894,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622176</v>
+        <v>622418</v>
       </c>
       <c r="R12" t="n">
-        <v>6616170</v>
+        <v>6616371</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1921,12 +1924,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2 hane och 4 hona</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1953,10 +1961,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121987023</v>
+        <v>121986570</v>
       </c>
       <c r="B13" t="n">
-        <v>98185</v>
+        <v>90809</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1965,42 +1973,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622167</v>
+        <v>622531</v>
       </c>
       <c r="R13" t="n">
-        <v>6616193</v>
+        <v>6616428</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2059,7 +2063,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121986572</v>
+        <v>121986571</v>
       </c>
       <c r="B14" t="n">
         <v>90809</v>
@@ -2099,10 +2103,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622558</v>
+        <v>622553</v>
       </c>
       <c r="R14" t="n">
-        <v>6616401</v>
+        <v>6616431</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2370,10 +2374,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121986492</v>
+        <v>121986554</v>
       </c>
       <c r="B17" t="n">
-        <v>58242</v>
+        <v>58232</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2386,34 +2390,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>208242</v>
+        <v>208250</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622554</v>
+        <v>622424</v>
       </c>
       <c r="R17" t="n">
-        <v>6616430</v>
+        <v>6616368</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2440,12 +2453,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,10 +2485,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121986571</v>
+        <v>121993752</v>
       </c>
       <c r="B18" t="n">
-        <v>90809</v>
+        <v>4770</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2484,25 +2497,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>100299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2512,10 +2525,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622553</v>
+        <v>622154</v>
       </c>
       <c r="R18" t="n">
-        <v>6616431</v>
+        <v>6616068</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2542,12 +2555,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2562,19 +2575,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121987017</v>
+        <v>121987026</v>
       </c>
       <c r="B19" t="n">
         <v>98185</v>
@@ -2609,7 +2622,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2618,10 +2631,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622176</v>
+        <v>622127</v>
       </c>
       <c r="R19" t="n">
-        <v>6616076</v>
+        <v>6616087</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2648,12 +2661,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2680,10 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121986550</v>
+        <v>121987017</v>
       </c>
       <c r="B20" t="n">
-        <v>58245</v>
+        <v>98185</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2692,38 +2705,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100141</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>622418</v>
+        <v>622176</v>
       </c>
       <c r="R20" t="n">
-        <v>6616372</v>
+        <v>6616076</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2750,12 +2767,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2782,10 +2799,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121987026</v>
+        <v>121986568</v>
       </c>
       <c r="B21" t="n">
-        <v>98185</v>
+        <v>100451</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2794,42 +2811,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>622127</v>
+        <v>622281</v>
       </c>
       <c r="R21" t="n">
-        <v>6616087</v>
+        <v>6616334</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2856,12 +2869,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2888,10 +2901,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121987024</v>
+        <v>121986552</v>
       </c>
       <c r="B22" t="n">
-        <v>98185</v>
+        <v>58245</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2900,42 +2913,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100141</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>622203</v>
+        <v>622418</v>
       </c>
       <c r="R22" t="n">
-        <v>6616185</v>
+        <v>6616370</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2962,12 +2971,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>1 hona</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2994,10 +3008,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121986551</v>
+        <v>121987024</v>
       </c>
       <c r="B23" t="n">
-        <v>58242</v>
+        <v>98185</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3006,35 +3020,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>208242</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3043,10 +3052,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>622418</v>
+        <v>622203</v>
       </c>
       <c r="R23" t="n">
-        <v>6616372</v>
+        <v>6616185</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3073,12 +3082,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3105,7 +3114,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121986553</v>
+        <v>121986551</v>
       </c>
       <c r="B24" t="n">
         <v>58242</v>
@@ -3140,7 +3149,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3157,7 +3166,7 @@
         <v>622418</v>
       </c>
       <c r="R24" t="n">
-        <v>6616371</v>
+        <v>6616372</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3190,11 +3199,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-04-29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>2 hane och 4 hona</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3221,10 +3225,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121986568</v>
+        <v>121986547</v>
       </c>
       <c r="B25" t="n">
-        <v>100451</v>
+        <v>58245</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3237,21 +3241,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>100141</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3261,10 +3265,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>622281</v>
+        <v>622415</v>
       </c>
       <c r="R25" t="n">
-        <v>6616334</v>
+        <v>6616365</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3291,12 +3295,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3323,10 +3332,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121986554</v>
+        <v>121993748</v>
       </c>
       <c r="B26" t="n">
-        <v>58232</v>
+        <v>95732</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3335,47 +3344,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>208250</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>622424</v>
+        <v>622274</v>
       </c>
       <c r="R26" t="n">
-        <v>6616368</v>
+        <v>6616320</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3402,12 +3402,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3422,22 +3422,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121993752</v>
+        <v>121993750</v>
       </c>
       <c r="B27" t="n">
-        <v>4770</v>
+        <v>5173</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3450,21 +3450,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>622154</v>
+        <v>622261</v>
       </c>
       <c r="R27" t="n">
-        <v>6616068</v>
+        <v>6616264</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 49848-2019 artfynd.xlsx
+++ b/artfynd/A 49848-2019 artfynd.xlsx
@@ -1327,10 +1327,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121986550</v>
+        <v>121986581</v>
       </c>
       <c r="B7" t="n">
-        <v>58245</v>
+        <v>90821</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1339,25 +1339,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100141</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>622418</v>
+        <v>622074</v>
       </c>
       <c r="R7" t="n">
-        <v>6616372</v>
+        <v>6616112</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1397,12 +1397,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>på död tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1429,10 +1434,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121987018</v>
+        <v>121986554</v>
       </c>
       <c r="B8" t="n">
-        <v>98185</v>
+        <v>58237</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1441,30 +1446,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>208250</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1473,10 +1483,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622176</v>
+        <v>622424</v>
       </c>
       <c r="R8" t="n">
-        <v>6616170</v>
+        <v>6616368</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1503,12 +1513,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1535,10 +1545,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121987023</v>
+        <v>121986549</v>
       </c>
       <c r="B9" t="n">
-        <v>98185</v>
+        <v>58250</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1547,42 +1557,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100141</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>622167</v>
+        <v>622418</v>
       </c>
       <c r="R9" t="n">
-        <v>6616193</v>
+        <v>6616372</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1609,12 +1615,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1 hona</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1641,10 +1652,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121986572</v>
+        <v>121986553</v>
       </c>
       <c r="B10" t="n">
-        <v>90809</v>
+        <v>58247</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1653,38 +1664,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>208242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>622558</v>
+        <v>622418</v>
       </c>
       <c r="R10" t="n">
-        <v>6616401</v>
+        <v>6616371</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1711,12 +1731,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2 hane och 4 hona</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1743,10 +1768,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121986492</v>
+        <v>121993752</v>
       </c>
       <c r="B11" t="n">
-        <v>58242</v>
+        <v>4770</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1759,21 +1784,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208242</v>
+        <v>100299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1783,10 +1808,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>622554</v>
+        <v>622154</v>
       </c>
       <c r="R11" t="n">
-        <v>6616430</v>
+        <v>6616068</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1813,12 +1838,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,22 +1858,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121986553</v>
+        <v>121987018</v>
       </c>
       <c r="B12" t="n">
-        <v>58242</v>
+        <v>98197</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1857,35 +1882,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208242</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1894,10 +1914,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622418</v>
+        <v>622176</v>
       </c>
       <c r="R12" t="n">
-        <v>6616371</v>
+        <v>6616170</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1924,17 +1944,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2 hane och 4 hona</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1961,10 +1976,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121986570</v>
+        <v>121986572</v>
       </c>
       <c r="B13" t="n">
-        <v>90809</v>
+        <v>90821</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2001,10 +2016,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622531</v>
+        <v>622558</v>
       </c>
       <c r="R13" t="n">
-        <v>6616428</v>
+        <v>6616401</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2066,7 +2081,7 @@
         <v>121986571</v>
       </c>
       <c r="B14" t="n">
-        <v>90809</v>
+        <v>90821</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2165,10 +2180,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121986581</v>
+        <v>121986570</v>
       </c>
       <c r="B15" t="n">
-        <v>90809</v>
+        <v>90821</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2205,10 +2220,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622074</v>
+        <v>622531</v>
       </c>
       <c r="R15" t="n">
-        <v>6616112</v>
+        <v>6616428</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,17 +2250,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>på död tall</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2272,10 +2282,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121986548</v>
+        <v>121986551</v>
       </c>
       <c r="B16" t="n">
-        <v>58232</v>
+        <v>58247</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2288,24 +2298,33 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
@@ -2374,10 +2393,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121986554</v>
+        <v>121986547</v>
       </c>
       <c r="B17" t="n">
-        <v>58232</v>
+        <v>58250</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2390,43 +2409,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>208250</v>
+        <v>100141</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622424</v>
+        <v>622415</v>
       </c>
       <c r="R17" t="n">
-        <v>6616368</v>
+        <v>6616365</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2459,6 +2469,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2485,10 +2500,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121993752</v>
+        <v>121987023</v>
       </c>
       <c r="B18" t="n">
-        <v>4770</v>
+        <v>98197</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2497,38 +2512,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622154</v>
+        <v>622167</v>
       </c>
       <c r="R18" t="n">
-        <v>6616068</v>
+        <v>6616193</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2555,12 +2574,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2575,22 +2594,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121987026</v>
+        <v>121987024</v>
       </c>
       <c r="B19" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2631,10 +2650,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622127</v>
+        <v>622203</v>
       </c>
       <c r="R19" t="n">
-        <v>6616087</v>
+        <v>6616185</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2661,12 +2680,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2693,10 +2712,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121987017</v>
+        <v>121993750</v>
       </c>
       <c r="B20" t="n">
-        <v>98185</v>
+        <v>5173</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2705,42 +2724,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>622176</v>
+        <v>622261</v>
       </c>
       <c r="R20" t="n">
-        <v>6616076</v>
+        <v>6616264</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2767,12 +2782,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2787,22 +2802,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121986568</v>
+        <v>121993748</v>
       </c>
       <c r="B21" t="n">
-        <v>100451</v>
+        <v>95744</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2811,25 +2826,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2839,10 +2854,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>622281</v>
+        <v>622274</v>
       </c>
       <c r="R21" t="n">
-        <v>6616334</v>
+        <v>6616320</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2869,12 +2884,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2889,22 +2904,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121986552</v>
+        <v>121986492</v>
       </c>
       <c r="B22" t="n">
-        <v>58245</v>
+        <v>58247</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2917,21 +2932,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100141</v>
+        <v>208242</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2941,10 +2956,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>622418</v>
+        <v>622554</v>
       </c>
       <c r="R22" t="n">
-        <v>6616370</v>
+        <v>6616430</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2971,17 +2986,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>1 hona</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3008,10 +3018,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121987024</v>
+        <v>121986548</v>
       </c>
       <c r="B23" t="n">
-        <v>98185</v>
+        <v>58237</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3020,42 +3030,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>208250</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>622203</v>
+        <v>622418</v>
       </c>
       <c r="R23" t="n">
-        <v>6616185</v>
+        <v>6616372</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3082,12 +3088,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3114,10 +3120,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121986551</v>
+        <v>121987017</v>
       </c>
       <c r="B24" t="n">
-        <v>58242</v>
+        <v>98197</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3126,35 +3132,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>208242</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3163,10 +3164,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>622418</v>
+        <v>622176</v>
       </c>
       <c r="R24" t="n">
-        <v>6616372</v>
+        <v>6616076</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3193,12 +3194,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3225,10 +3226,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121986547</v>
+        <v>121986552</v>
       </c>
       <c r="B25" t="n">
-        <v>58245</v>
+        <v>58250</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3265,10 +3266,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>622415</v>
+        <v>622418</v>
       </c>
       <c r="R25" t="n">
-        <v>6616365</v>
+        <v>6616370</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3305,7 +3306,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>1 hona</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3332,10 +3333,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121993748</v>
+        <v>121987026</v>
       </c>
       <c r="B26" t="n">
-        <v>95732</v>
+        <v>98197</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3344,38 +3345,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>622274</v>
+        <v>622127</v>
       </c>
       <c r="R26" t="n">
-        <v>6616320</v>
+        <v>6616087</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3402,12 +3407,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3422,22 +3427,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121993750</v>
+        <v>121986568</v>
       </c>
       <c r="B27" t="n">
-        <v>5173</v>
+        <v>100463</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3450,21 +3455,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3474,10 +3479,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>622261</v>
+        <v>622281</v>
       </c>
       <c r="R27" t="n">
-        <v>6616264</v>
+        <v>6616334</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3504,12 +3509,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3524,12 +3529,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 49848-2019 artfynd.xlsx
+++ b/artfynd/A 49848-2019 artfynd.xlsx
@@ -1327,10 +1327,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121986581</v>
+        <v>121986570</v>
       </c>
       <c r="B7" t="n">
-        <v>90821</v>
+        <v>90828</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>622074</v>
+        <v>622531</v>
       </c>
       <c r="R7" t="n">
-        <v>6616112</v>
+        <v>6616428</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1397,17 +1397,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>på död tall</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1434,10 +1429,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121986554</v>
+        <v>121986568</v>
       </c>
       <c r="B8" t="n">
-        <v>58237</v>
+        <v>100468</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1450,43 +1445,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208250</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622424</v>
+        <v>622281</v>
       </c>
       <c r="R8" t="n">
-        <v>6616368</v>
+        <v>6616334</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1513,12 +1499,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1545,10 +1531,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121986549</v>
+        <v>121987017</v>
       </c>
       <c r="B9" t="n">
-        <v>58250</v>
+        <v>98202</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1557,38 +1543,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100141</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>622418</v>
+        <v>622176</v>
       </c>
       <c r="R9" t="n">
-        <v>6616372</v>
+        <v>6616076</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1615,17 +1605,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>1 hona</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1652,10 +1637,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121986553</v>
+        <v>121993750</v>
       </c>
       <c r="B10" t="n">
-        <v>58247</v>
+        <v>5173</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1668,43 +1653,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208242</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>622418</v>
+        <v>622261</v>
       </c>
       <c r="R10" t="n">
-        <v>6616371</v>
+        <v>6616264</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1731,17 +1707,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2 hane och 4 hona</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1756,22 +1727,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121993752</v>
+        <v>121986554</v>
       </c>
       <c r="B11" t="n">
-        <v>4770</v>
+        <v>58237</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1784,34 +1755,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100299</v>
+        <v>208250</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>622154</v>
+        <v>622424</v>
       </c>
       <c r="R11" t="n">
-        <v>6616068</v>
+        <v>6616368</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1838,12 +1818,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1858,22 +1838,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121987018</v>
+        <v>121986551</v>
       </c>
       <c r="B12" t="n">
-        <v>98197</v>
+        <v>58247</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1882,30 +1862,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>208242</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1914,10 +1899,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622176</v>
+        <v>622418</v>
       </c>
       <c r="R12" t="n">
-        <v>6616170</v>
+        <v>6616372</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1944,12 +1929,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1976,10 +1961,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121986572</v>
+        <v>121986550</v>
       </c>
       <c r="B13" t="n">
-        <v>90821</v>
+        <v>58250</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1988,25 +1973,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>100141</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2016,10 +2001,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622558</v>
+        <v>622418</v>
       </c>
       <c r="R13" t="n">
-        <v>6616401</v>
+        <v>6616372</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2046,12 +2031,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2078,10 +2063,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121986571</v>
+        <v>121986572</v>
       </c>
       <c r="B14" t="n">
-        <v>90821</v>
+        <v>90828</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2118,10 +2103,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622553</v>
+        <v>622558</v>
       </c>
       <c r="R14" t="n">
-        <v>6616431</v>
+        <v>6616401</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2180,10 +2165,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121986570</v>
+        <v>121986581</v>
       </c>
       <c r="B15" t="n">
-        <v>90821</v>
+        <v>90828</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2220,10 +2205,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622531</v>
+        <v>622074</v>
       </c>
       <c r="R15" t="n">
-        <v>6616428</v>
+        <v>6616112</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2250,12 +2235,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>på död tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,10 +2272,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121986551</v>
+        <v>121987024</v>
       </c>
       <c r="B16" t="n">
-        <v>58247</v>
+        <v>98202</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2294,35 +2284,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208242</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2331,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622418</v>
+        <v>622203</v>
       </c>
       <c r="R16" t="n">
-        <v>6616372</v>
+        <v>6616185</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2361,12 +2346,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2500,10 +2485,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121987023</v>
+        <v>121993752</v>
       </c>
       <c r="B18" t="n">
-        <v>98197</v>
+        <v>4770</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2512,42 +2497,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622167</v>
+        <v>622154</v>
       </c>
       <c r="R18" t="n">
-        <v>6616193</v>
+        <v>6616068</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2574,12 +2555,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2594,22 +2575,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121987024</v>
+        <v>121987023</v>
       </c>
       <c r="B19" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2650,10 +2631,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622203</v>
+        <v>622167</v>
       </c>
       <c r="R19" t="n">
-        <v>6616185</v>
+        <v>6616193</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2712,10 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121993750</v>
+        <v>121986553</v>
       </c>
       <c r="B20" t="n">
-        <v>5173</v>
+        <v>58247</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2728,34 +2709,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>208242</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>622261</v>
+        <v>622418</v>
       </c>
       <c r="R20" t="n">
-        <v>6616264</v>
+        <v>6616371</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2782,12 +2772,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2 hane och 4 hona</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2802,12 +2797,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2817,7 +2812,7 @@
         <v>121993748</v>
       </c>
       <c r="B21" t="n">
-        <v>95744</v>
+        <v>95749</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2916,10 +2911,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121986492</v>
+        <v>121986571</v>
       </c>
       <c r="B22" t="n">
-        <v>58247</v>
+        <v>90828</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2928,25 +2923,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>208242</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2956,10 +2951,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>622554</v>
+        <v>622553</v>
       </c>
       <c r="R22" t="n">
-        <v>6616430</v>
+        <v>6616431</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2986,12 +2981,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3120,10 +3115,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121987017</v>
+        <v>121987018</v>
       </c>
       <c r="B24" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3155,7 +3150,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3167,7 +3162,7 @@
         <v>622176</v>
       </c>
       <c r="R24" t="n">
-        <v>6616076</v>
+        <v>6616170</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3226,10 +3221,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121986552</v>
+        <v>121986492</v>
       </c>
       <c r="B25" t="n">
-        <v>58250</v>
+        <v>58247</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3242,21 +3237,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100141</v>
+        <v>208242</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3266,10 +3261,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>622418</v>
+        <v>622554</v>
       </c>
       <c r="R25" t="n">
-        <v>6616370</v>
+        <v>6616430</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3296,17 +3291,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>1 hona</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3336,7 +3326,7 @@
         <v>121987026</v>
       </c>
       <c r="B26" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3439,10 +3429,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121986568</v>
+        <v>121986552</v>
       </c>
       <c r="B27" t="n">
-        <v>100463</v>
+        <v>58250</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3455,21 +3445,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>100141</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3479,10 +3469,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>622281</v>
+        <v>622418</v>
       </c>
       <c r="R27" t="n">
-        <v>6616334</v>
+        <v>6616370</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3509,12 +3499,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1 hona</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 49848-2019 artfynd.xlsx
+++ b/artfynd/A 49848-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1202,10 +1202,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113619086</v>
+        <v>121986570</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
+        <v>90828</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1214,50 +1214,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bårskärskogen Savlinge 1:1, Upl</t>
+          <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>622100</v>
+        <v>622531</v>
       </c>
       <c r="R6" t="n">
-        <v>6616006</v>
+        <v>6616428</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1279,24 +1270,14 @@
           <t>Härkeberga</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>C-Enk-0500</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2005-05-13</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2005-05-13</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gammal granskog med mkt stor förekomst av knärot och grönpyrola.</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1311,26 +1292,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ingvar Sundh</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Emma Hellkvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121986570</v>
+        <v>121986568</v>
       </c>
       <c r="B7" t="n">
-        <v>90828</v>
+        <v>100468</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1339,25 +1316,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1367,10 +1344,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>622531</v>
+        <v>622281</v>
       </c>
       <c r="R7" t="n">
-        <v>6616428</v>
+        <v>6616334</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1429,10 +1406,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121986568</v>
+        <v>121987017</v>
       </c>
       <c r="B8" t="n">
-        <v>100468</v>
+        <v>98202</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1441,38 +1418,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622281</v>
+        <v>622176</v>
       </c>
       <c r="R8" t="n">
-        <v>6616334</v>
+        <v>6616076</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1499,12 +1480,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121987017</v>
+        <v>121993750</v>
       </c>
       <c r="B9" t="n">
-        <v>98202</v>
+        <v>5173</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1543,42 +1524,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>622176</v>
+        <v>622261</v>
       </c>
       <c r="R9" t="n">
-        <v>6616076</v>
+        <v>6616264</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1605,12 +1582,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1625,22 +1602,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121993750</v>
+        <v>121986554</v>
       </c>
       <c r="B10" t="n">
-        <v>5173</v>
+        <v>58237</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1653,34 +1630,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>208250</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>622261</v>
+        <v>622424</v>
       </c>
       <c r="R10" t="n">
-        <v>6616264</v>
+        <v>6616368</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1707,12 +1693,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,22 +1713,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121986554</v>
+        <v>121986551</v>
       </c>
       <c r="B11" t="n">
-        <v>58237</v>
+        <v>58247</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1755,26 +1741,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1788,10 +1774,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>622424</v>
+        <v>622418</v>
       </c>
       <c r="R11" t="n">
-        <v>6616368</v>
+        <v>6616372</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1850,10 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121986551</v>
+        <v>121986550</v>
       </c>
       <c r="B12" t="n">
-        <v>58247</v>
+        <v>58250</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1866,33 +1852,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
@@ -1961,10 +1938,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121986550</v>
+        <v>121986572</v>
       </c>
       <c r="B13" t="n">
-        <v>58250</v>
+        <v>90828</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1973,25 +1950,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100141</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2001,10 +1978,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622418</v>
+        <v>622558</v>
       </c>
       <c r="R13" t="n">
-        <v>6616372</v>
+        <v>6616401</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2031,12 +2008,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2063,7 +2040,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121986572</v>
+        <v>121986581</v>
       </c>
       <c r="B14" t="n">
         <v>90828</v>
@@ -2103,10 +2080,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622558</v>
+        <v>622074</v>
       </c>
       <c r="R14" t="n">
-        <v>6616401</v>
+        <v>6616112</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,12 +2110,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>på död tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,10 +2147,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121986581</v>
+        <v>121987024</v>
       </c>
       <c r="B15" t="n">
-        <v>90828</v>
+        <v>98202</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2177,38 +2159,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622074</v>
+        <v>622203</v>
       </c>
       <c r="R15" t="n">
-        <v>6616112</v>
+        <v>6616185</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,17 +2221,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>på död tall</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2272,10 +2253,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121987024</v>
+        <v>121986547</v>
       </c>
       <c r="B16" t="n">
-        <v>98202</v>
+        <v>58250</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2284,42 +2265,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100141</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622203</v>
+        <v>622415</v>
       </c>
       <c r="R16" t="n">
-        <v>6616185</v>
+        <v>6616365</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,12 +2323,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2378,10 +2360,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121986547</v>
+        <v>121993752</v>
       </c>
       <c r="B17" t="n">
-        <v>58250</v>
+        <v>4770</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2394,21 +2376,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100141</v>
+        <v>100299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2418,10 +2400,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622415</v>
+        <v>622154</v>
       </c>
       <c r="R17" t="n">
-        <v>6616365</v>
+        <v>6616068</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2448,17 +2430,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2473,22 +2450,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121993752</v>
+        <v>121987023</v>
       </c>
       <c r="B18" t="n">
-        <v>4770</v>
+        <v>98202</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2497,38 +2474,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622154</v>
+        <v>622167</v>
       </c>
       <c r="R18" t="n">
-        <v>6616068</v>
+        <v>6616193</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2555,12 +2536,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2575,22 +2556,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121987023</v>
+        <v>121986553</v>
       </c>
       <c r="B19" t="n">
-        <v>98202</v>
+        <v>58247</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2599,30 +2580,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>208242</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2631,10 +2617,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622167</v>
+        <v>622418</v>
       </c>
       <c r="R19" t="n">
-        <v>6616193</v>
+        <v>6616371</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2661,12 +2647,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2 hane och 4 hona</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2693,10 +2684,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121986553</v>
+        <v>121993748</v>
       </c>
       <c r="B20" t="n">
-        <v>58247</v>
+        <v>95749</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2705,47 +2696,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>208242</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>622418</v>
+        <v>622274</v>
       </c>
       <c r="R20" t="n">
-        <v>6616371</v>
+        <v>6616320</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2772,17 +2754,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>2 hane och 4 hona</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2797,22 +2774,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Emma Hellkvist</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121993748</v>
+        <v>121986571</v>
       </c>
       <c r="B21" t="n">
-        <v>95749</v>
+        <v>90828</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2825,21 +2802,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2849,10 +2826,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>622274</v>
+        <v>622553</v>
       </c>
       <c r="R21" t="n">
-        <v>6616320</v>
+        <v>6616431</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2879,12 +2856,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2899,22 +2876,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Emma Hellkvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121986571</v>
+        <v>121986548</v>
       </c>
       <c r="B22" t="n">
-        <v>90828</v>
+        <v>58237</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2923,25 +2900,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>208250</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2951,10 +2928,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>622553</v>
+        <v>622418</v>
       </c>
       <c r="R22" t="n">
-        <v>6616431</v>
+        <v>6616372</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2981,12 +2958,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3013,10 +2990,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121986548</v>
+        <v>121987018</v>
       </c>
       <c r="B23" t="n">
-        <v>58237</v>
+        <v>98202</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3025,38 +3002,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>208250</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>622418</v>
+        <v>622176</v>
       </c>
       <c r="R23" t="n">
-        <v>6616372</v>
+        <v>6616170</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3083,12 +3064,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3115,10 +3096,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121987018</v>
+        <v>121986492</v>
       </c>
       <c r="B24" t="n">
-        <v>98202</v>
+        <v>58247</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3127,42 +3108,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>208242</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>622176</v>
+        <v>622554</v>
       </c>
       <c r="R24" t="n">
-        <v>6616170</v>
+        <v>6616430</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3189,12 +3166,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3221,10 +3198,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121986492</v>
+        <v>121987026</v>
       </c>
       <c r="B25" t="n">
-        <v>58247</v>
+        <v>98202</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3233,38 +3210,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>208242</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>622554</v>
+        <v>622127</v>
       </c>
       <c r="R25" t="n">
-        <v>6616430</v>
+        <v>6616087</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3291,12 +3272,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3323,10 +3304,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121987026</v>
+        <v>121986552</v>
       </c>
       <c r="B26" t="n">
-        <v>98202</v>
+        <v>58250</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3335,42 +3316,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100141</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sneby bergtäkt, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>622127</v>
+        <v>622418</v>
       </c>
       <c r="R26" t="n">
-        <v>6616087</v>
+        <v>6616370</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3397,12 +3374,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1 hona</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3426,113 +3408,6 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>121986552</v>
-      </c>
-      <c r="B27" t="n">
-        <v>58250</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>100141</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Större vattensalamander</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Triturus cristatus</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Laurenti, 1768)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Sneby bergtäkt, Upl</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>622418</v>
-      </c>
-      <c r="R27" t="n">
-        <v>6616370</v>
-      </c>
-      <c r="S27" t="n">
-        <v>10</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Enköping</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Härkeberga</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2024-04-29</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2024-04-29</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>1 hona</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Emma Hellkvist</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Emma Hellkvist</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
